--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/12,10,26 Останкино КИ и ЗПФ/дв 12,10,26 лгрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/12,10,26 Останкино КИ и ЗПФ/дв 12,10,26 лгрсч ост ки.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\РАБОЧИЙ СТОЛ\расчеты Останкино КИ и ЗПФ\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\12,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CF0C8348-6E7A-490C-9F55-A2AE3A2AA2BE}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD9F564-A3A1-4C76-8F3A-6736E100E40A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="404" uniqueCount="164">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="405" uniqueCount="166">
   <si>
     <t>Номенклатура</t>
   </si>
@@ -527,6 +527,12 @@
   <si>
     <t>100кг (письмом)</t>
   </si>
+  <si>
+    <t>РАЗОВО / АСЛАМ</t>
+  </si>
+  <si>
+    <t>отдельным бланком</t>
+  </si>
 </sst>
 </file>
 
@@ -663,7 +669,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="164" fontId="3" fillId="2" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1"/>
@@ -686,6 +692,7 @@
     <xf numFmtId="164" fontId="1" fillId="5" borderId="1" xfId="1" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Arial10px" xfId="1" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
@@ -13009,7 +13016,7 @@
       </c>
       <c r="Q71" s="4"/>
       <c r="R71" s="4">
-        <f t="shared" ref="R71:R103" si="19">ROUND(Q71,0)</f>
+        <f t="shared" ref="R71:R102" si="19">ROUND(Q71,0)</f>
         <v>0</v>
       </c>
       <c r="S71" s="20"/>
@@ -16552,8 +16559,8 @@
       <c r="H103" s="8">
         <v>45</v>
       </c>
-      <c r="I103" s="8" t="s">
-        <v>76</v>
+      <c r="I103" s="22" t="s">
+        <v>164</v>
       </c>
       <c r="J103" s="8"/>
       <c r="K103" s="8"/>
@@ -16610,7 +16617,9 @@
       <c r="AE103" s="8">
         <v>0</v>
       </c>
-      <c r="AF103" s="8"/>
+      <c r="AF103" s="8" t="s">
+        <v>165</v>
+      </c>
       <c r="AG103" s="8">
         <f t="shared" si="21"/>
         <v>98.399999999999991</v>

--- a/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/12,10,26 Останкино КИ и ЗПФ/дв 12,10,26 лгрсч ост ки.xlsx
+++ b/2026/ЗАВОДЫ/Останкино/филиалы НВ/10,26/12,10,26 Останкино КИ и ЗПФ/дв 12,10,26 лгрсч ост ки.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\WORK\2025_05\2026\ЗАВОДЫ\Останкино\филиалы НВ\10,26\12,10,26 Останкино КИ и ЗПФ\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FFD9F564-A3A1-4C76-8F3A-6736E100E40A}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{678D1893-28BF-4E78-A2F8-F55226FC701E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -7435,7 +7435,7 @@
       <c r="AE22" s="8">
         <v>78.400000000000006</v>
       </c>
-      <c r="AF22" s="9" t="s">
+      <c r="AF22" s="22" t="s">
         <v>156</v>
       </c>
       <c r="AG22" s="8">
@@ -16182,7 +16182,7 @@
       <c r="AE99" s="8">
         <v>0</v>
       </c>
-      <c r="AF99" s="9" t="s">
+      <c r="AF99" s="22" t="s">
         <v>150</v>
       </c>
       <c r="AG99" s="8">
